--- a/output/pdf_financials_xlsx/ESAU.xlsx
+++ b/output/pdf_financials_xlsx/ESAU.xlsx
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.559412</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.757632</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.6098</v>
       </c>
     </row>
     <row r="93">
@@ -3218,7 +3218,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -3716,7 +3720,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>1.559412</v>
       </c>

--- a/output/pdf_financials_xlsx/ESAU.xlsx
+++ b/output/pdf_financials_xlsx/ESAU.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.080349</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.137008</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.90974</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.080349</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.137008</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.90974</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.145373</v>
+        <v>0.065024</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.151381</v>
+        <v>0.014373</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.07037</v>
+        <v>0.16063</v>
       </c>
     </row>
     <row r="49">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">

--- a/output/pdf_financials_xlsx/ESAU.xlsx
+++ b/output/pdf_financials_xlsx/ESAU.xlsx
@@ -5094,7 +5094,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>1.9935</v>
       </c>
